--- a/Contribution Summary - Final.xlsx
+++ b/Contribution Summary - Final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marfe\Desktop\Courses\Semester 2\Applied Database Technologies\Project\ADT-Final-Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8207bcd4c4ed8cf/Masters of Data Science/DSCI-D532/Final Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EDCC20-662A-4C25-A7A8-F1B77FDCB02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E81E1E6-B2C5-422A-A58A-877EEE86EC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{248FD177-A6C4-4547-84A7-5795F7ADDF04}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{248FD177-A6C4-4547-84A7-5795F7ADDF04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Name</t>
   </si>
@@ -122,9 +122,6 @@
     <t>refine formatting and clarity of notes on technical build part of the project</t>
   </si>
   <si>
-    <t>data engineering features and cloud architecture services to offer expansion plans</t>
-  </si>
-  <si>
     <t>Used hyperlinks</t>
   </si>
   <si>
@@ -141,6 +138,30 @@
   </si>
   <si>
     <t>Description of team reflections on what we learned during this project and the most interesting parts</t>
+  </si>
+  <si>
+    <t>Edit and Finalize Presentation</t>
+  </si>
+  <si>
+    <t>Organize Presentation</t>
+  </si>
+  <si>
+    <t>Record introduction and project demo</t>
+  </si>
+  <si>
+    <t>Data engineering features and cloud architecture services to offer expansion plans</t>
+  </si>
+  <si>
+    <t>Edited slides and planned project demo</t>
+  </si>
+  <si>
+    <t>Plan, order, and format one dashboard in Quicksight</t>
+  </si>
+  <si>
+    <t>Wrote, tested, and added query examples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drafted, edited </t>
   </si>
 </sst>
 </file>
@@ -187,9 +208,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -199,10 +226,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,228 +574,265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E5930CB-B72E-40EA-8130-98E5544941A0}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7">
+      <c r="D8" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9">
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="3">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3">
         <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16">
-        <v>1.5</v>
       </c>
     </row>
   </sheetData>
